--- a/artfynd/A 58890-2022 artfynd.xlsx
+++ b/artfynd/A 58890-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58890-2022 artfynd.xlsx
+++ b/artfynd/A 58890-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1676494</v>
+        <v>818142</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>307179.696678215</v>
+        <v>307180</v>
       </c>
       <c r="R2" t="n">
-        <v>6500525.780437236</v>
+        <v>6500526</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2012-09-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,245 +774,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>818142</v>
-      </c>
-      <c r="B3" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2569</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Stor revmossa</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Bazzania trilobata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Orredalen, 525 m SSO, Boh</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>307179.696678215</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6500525.780437236</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Munkedal</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Svarteborg</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2012-09-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2012-09-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bäckravin med fuktig granskog</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Crister Albinsson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Crister Albinsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>6991089</v>
-      </c>
-      <c r="B4" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Kynnefjäll, Orredalen, Boh</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>307126.637783621</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6500541.9782257</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Munkedal</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Svarteborg</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2013-09-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2013-09-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Studio Fungorum</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrskog i bäckravin</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Anita Stridvall</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Mikael Jeppson, Anita Stridvall</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58890-2022 artfynd.xlsx
+++ b/artfynd/A 58890-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,8 +779,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/818142</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>